--- a/forms/trg/Formulir_TRG_malvecsis.xlsx
+++ b/forms/trg/Formulir_TRG_malvecsis.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. dr. Syafruddin, PhD</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Department of Parasitology, Faculty of Medicine, Universitas Hasanuddin</t>
@@ -1021,7 +1025,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1058,7 +1062,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1095,7 +1099,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1169,7 +1173,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1202,7 +1206,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1235,7 +1239,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1301,7 +1305,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1334,7 +1338,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
